--- a/public/templates/Mammography_Test_Data_Template_NoTimer.xlsx
+++ b/public/templates/Mammography_Test_Data_Template_NoTimer.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1193,25 +1193,25 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>FDD (cm)</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B22" t="str">
-        <v>kV</v>
+        <v>&lt;=</v>
       </c>
       <c r="C22" t="str">
-        <v>mAs</v>
+        <v/>
       </c>
       <c r="D22" t="str">
-        <v>Measured Output 1</v>
+        <v/>
       </c>
       <c r="E22" t="str">
-        <v>Measured Output 2</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>Measured Output 3</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>Tolerance</v>
+        <v/>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1237,25 +1237,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>65</v>
+        <v>Tolerance Value (CoV)</v>
       </c>
       <c r="B23" t="str">
-        <v>25</v>
+        <v>0.05</v>
       </c>
       <c r="C23" t="str">
-        <v>25</v>
+        <v/>
       </c>
       <c r="D23" t="str">
-        <v>10.5</v>
+        <v/>
       </c>
       <c r="E23" t="str">
-        <v>10.4</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v>10.6</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1281,22 +1281,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>FDD (cm)</v>
       </c>
       <c r="B24" t="str">
-        <v>28</v>
+        <v>kV</v>
       </c>
       <c r="C24" t="str">
-        <v>25</v>
+        <v>mAs</v>
       </c>
       <c r="D24" t="str">
-        <v>12.1</v>
+        <v>Measured Output 1</v>
       </c>
       <c r="E24" t="str">
-        <v>12.0</v>
+        <v>Measured Output 2</v>
       </c>
       <c r="F24" t="str">
-        <v>12.2</v>
+        <v>Measured Output 3</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1325,22 +1325,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>65</v>
       </c>
       <c r="B25" t="str">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C25" t="str">
         <v>25</v>
       </c>
       <c r="D25" t="str">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="E25" t="str">
-        <v>14.4</v>
+        <v>10.4</v>
       </c>
       <c r="F25" t="str">
-        <v>14.6</v>
+        <v>10.6</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1372,19 +1372,19 @@
         <v/>
       </c>
       <c r="B26" t="str">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C26" t="str">
         <v>25</v>
       </c>
       <c r="D26" t="str">
-        <v>16.2</v>
+        <v>12.1</v>
       </c>
       <c r="E26" t="str">
-        <v>16.1</v>
+        <v>12.0</v>
       </c>
       <c r="F26" t="str">
-        <v>16.3</v>
+        <v>12.2</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1416,19 +1416,19 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C27" t="str">
         <v>25</v>
       </c>
       <c r="D27" t="str">
-        <v>18.0</v>
+        <v>14.5</v>
       </c>
       <c r="E27" t="str">
-        <v>17.9</v>
+        <v>14.4</v>
       </c>
       <c r="F27" t="str">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1452,27 +1452,71 @@
         <v/>
       </c>
       <c r="N27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <v>40</v>
+      </c>
+      <c r="C28" t="str">
+        <v>25</v>
+      </c>
+      <c r="D28" t="str">
+        <v>16.2</v>
+      </c>
+      <c r="E28" t="str">
+        <v>16.1</v>
+      </c>
+      <c r="F28" t="str">
+        <v>16.3</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL</v>
+        <v/>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>49</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>25</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>18.0</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>17.9</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>18.1</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1497,152 +1541,149 @@
       </c>
       <c r="N29" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>FDD (cm)</v>
-      </c>
-      <c r="B30" t="str">
-        <v>kV</v>
-      </c>
-      <c r="C30" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Time (Sec)</v>
-      </c>
-      <c r="E30" t="str">
-        <v>Workload</v>
-      </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v>Tol Value</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Tol Operator</v>
-      </c>
-      <c r="I30" t="str">
-        <v>Tol Time</v>
-      </c>
-      <c r="J30" t="str">
-        <v>Location</v>
-      </c>
-      <c r="K30" t="str">
-        <v>Left</v>
-      </c>
-      <c r="L30" t="str">
-        <v>Right</v>
-      </c>
-      <c r="M30" t="str">
-        <v>Front</v>
-      </c>
-      <c r="N30" t="str">
-        <v>Back</v>
-      </c>
-      <c r="O30" t="str">
-        <v>Top</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>100</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL</v>
       </c>
       <c r="B31" t="str">
-        <v>120</v>
+        <v/>
       </c>
       <c r="C31" t="str">
-        <v>21</v>
+        <v/>
       </c>
       <c r="D31" t="str">
-        <v>2</v>
+        <v/>
       </c>
       <c r="E31" t="str">
-        <v>500</v>
+        <v/>
       </c>
       <c r="F31" t="str">
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H31" t="str">
-        <v>&lt;=</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="J31" t="str">
-        <v>TUBE</v>
+        <v/>
       </c>
       <c r="K31" t="str">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="L31" t="str">
-        <v>0.03</v>
+        <v/>
       </c>
       <c r="M31" t="str">
-        <v>0.06</v>
+        <v/>
       </c>
       <c r="N31" t="str">
-        <v>0.04</v>
-      </c>
-      <c r="O31" t="str">
-        <v>0.02</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>FDD (cm)</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>kV</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>mA</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>Time (Sec)</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>Workload</v>
       </c>
       <c r="F32" t="str">
         <v/>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>Tol Value</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>Tol Operator</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Tol Time</v>
       </c>
       <c r="J32" t="str">
-        <v>COLLIMATOR</v>
+        <v>Location</v>
       </c>
       <c r="K32" t="str">
+        <v>Left</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Right</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Front</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Back</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Top</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>100</v>
+      </c>
+      <c r="B33" t="str">
+        <v>120</v>
+      </c>
+      <c r="C33" t="str">
+        <v>21</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2</v>
+      </c>
+      <c r="E33" t="str">
+        <v>500</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>1</v>
+      </c>
+      <c r="H33" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="I33" t="str">
+        <v>1</v>
+      </c>
+      <c r="J33" t="str">
+        <v>TUBE</v>
+      </c>
+      <c r="K33" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="L33" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="M33" t="str">
+        <v>0.06</v>
+      </c>
+      <c r="N33" t="str">
+        <v>0.04</v>
+      </c>
+      <c r="O33" t="str">
         <v>0.02</v>
-      </c>
-      <c r="L32" t="str">
-        <v>0.02</v>
-      </c>
-      <c r="M32" t="str">
-        <v>0.03</v>
-      </c>
-      <c r="N32" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="O32" t="str">
-        <v>0.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>TEST: IMAGING PHANTOM</v>
+        <v/>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -1669,77 +1710,36 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>COLLIMATOR</v>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="L34" t="str">
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>0.03</v>
       </c>
       <c r="N34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Visible Count</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Tol Operator</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Tol Value</v>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v/>
-      </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
-      <c r="I35" t="str">
-        <v/>
-      </c>
-      <c r="J35" t="str">
-        <v/>
-      </c>
-      <c r="K35" t="str">
-        <v/>
-      </c>
-      <c r="L35" t="str">
-        <v/>
-      </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
-      <c r="N35" t="str">
-        <v/>
+        <v>0.01</v>
+      </c>
+      <c r="O34" t="str">
+        <v>0.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Fibers</v>
+        <v>TEST: IMAGING PHANTOM</v>
       </c>
       <c r="B36" t="str">
-        <v>5</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v>&gt;=</v>
+        <v/>
       </c>
       <c r="D36" t="str">
-        <v>4</v>
+        <v/>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Micro Calcification</v>
+        <v>Name</v>
       </c>
       <c r="B37" t="str">
-        <v>6</v>
+        <v>Visible Count</v>
       </c>
       <c r="C37" t="str">
-        <v>&gt;=</v>
+        <v>Tol Operator</v>
       </c>
       <c r="D37" t="str">
-        <v>6</v>
+        <v>Tol Value</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1818,16 +1818,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Masses</v>
+        <v>Fibers</v>
       </c>
       <c r="B38" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="str">
         <v>&gt;=</v>
       </c>
       <c r="D38" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1857,21 +1857,65 @@
         <v/>
       </c>
       <c r="N38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Micro Calcification</v>
+      </c>
+      <c r="B39" t="str">
+        <v>6</v>
+      </c>
+      <c r="C39" t="str">
+        <v>&gt;=</v>
+      </c>
+      <c r="D39" t="str">
+        <v>6</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY</v>
+        <v>Masses</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>4</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>&gt;=</v>
       </c>
       <c r="D40" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1901,83 +1945,39 @@
         <v/>
       </c>
       <c r="N40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v/>
-      </c>
-      <c r="B41" t="str">
-        <v/>
-      </c>
-      <c r="C41" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D41" t="str">
-        <v>kV</v>
-      </c>
-      <c r="E41" t="str">
-        <v>Time</v>
-      </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v>Workload</v>
-      </c>
-      <c r="H41" t="str">
-        <v>Location</v>
-      </c>
-      <c r="I41" t="str">
-        <v>mR/hr</v>
-      </c>
-      <c r="J41" t="str">
-        <v>Category</v>
-      </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-      <c r="N41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v/>
+        <v>TEST: RADIATION PROTECTION SURVEY</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="D42" t="str">
-        <v>80</v>
+        <v/>
       </c>
       <c r="E42" t="str">
-        <v>0.5</v>
+        <v/>
       </c>
       <c r="F42" t="str">
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>300</v>
+        <v/>
       </c>
       <c r="H42" t="str">
-        <v>Control Console (Operator Position)</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="J42" t="str">
-        <v>worker</v>
+        <v/>
       </c>
       <c r="K42" t="str">
         <v/>
@@ -2000,28 +2000,28 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>mA</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>kV</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>Time</v>
       </c>
       <c r="F43" t="str">
         <v/>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>Workload</v>
       </c>
       <c r="H43" t="str">
-        <v>Outside Lead Glass</v>
+        <v>Location</v>
       </c>
       <c r="I43" t="str">
-        <v>0.03</v>
+        <v>mR/hr</v>
       </c>
       <c r="J43" t="str">
-        <v>worker</v>
+        <v>Category</v>
       </c>
       <c r="K43" t="str">
         <v/>
@@ -2044,28 +2044,28 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>100</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="F44" t="str">
         <v/>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>300</v>
       </c>
       <c r="H44" t="str">
-        <v>Outside Patient Entrance Door</v>
+        <v>Control Console (Operator Position)</v>
       </c>
       <c r="I44" t="str">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="J44" t="str">
-        <v>public</v>
+        <v>worker</v>
       </c>
       <c r="K44" t="str">
         <v/>
@@ -2103,30 +2103,118 @@
         <v/>
       </c>
       <c r="H45" t="str">
+        <v>Outside Lead Glass</v>
+      </c>
+      <c r="I45" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="J45" t="str">
+        <v>worker</v>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>Outside Patient Entrance Door</v>
+      </c>
+      <c r="I46" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="J46" t="str">
+        <v>public</v>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
         <v>Patient Waiting Area</v>
       </c>
-      <c r="I45" t="str">
+      <c r="I47" t="str">
         <v>0.01</v>
       </c>
-      <c r="J45" t="str">
+      <c r="J47" t="str">
         <v>public</v>
       </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O47"/>
   </ignoredErrors>
 </worksheet>
 </file>